--- a/src/s3/client_documents/1777454047886-BHEL_Questions.xlsx
+++ b/src/s3/client_documents/1777454047886-BHEL_Questions.xlsx
@@ -1,146 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arvind\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44959D65-0599-44B3-BC3D-1082B433869A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E88878D2-8F11-458A-994A-4126413E1ABA}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>questions</t>
-  </si>
-  <si>
-    <t>answer</t>
-  </si>
-  <si>
-    <t>page_num</t>
-  </si>
-  <si>
-    <t>source_text</t>
-  </si>
-  <si>
-    <t>topic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    reterive the primary ntity or project name from the document metadata?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    reterive the scope for painting specifications?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the stream parameters such as flow, temperature, and pressure?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the water parameters such as flow, temperature, and pressure?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    reterive Techcnical data from the general data of item?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the operating and mechanical data for the stream condition rating?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the operating and mechanical data for the stream condition size?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What is the spray water body material?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What is the spray water trim?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What is the spray water size?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    reterivet the technical table data of spray water actuator and their types,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the accessories?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the inspection and NDT requirements?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the buyer’s terms of payment?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What is the SSC delivery schedule?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What is included in the price format?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What is the warranty for SSC?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the contractor liquidated damages?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the quality control and inspection testing?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    reterive the data fro approval?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What are the packing and dispatch requirements for bidders?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    What is the compliance certificate for Clause 20(B)?,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    reterive the pre-qulification of independent laboratory,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    reterive the compensation damages,</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -159,21 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -493,151 +439,543 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2216EB6A-6689-455F-90A2-E812DD273801}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.77734375" customWidth="1"/>
-    <col min="2" max="2" width="65.33203125" customWidth="1"/>
-    <col min="3" max="4" width="31.21875" customWidth="1"/>
-    <col min="5" max="5" width="29.21875" customWidth="1"/>
+    <col width="21.77734375" customWidth="1" min="1" max="1"/>
+    <col width="65.33203125" customWidth="1" min="2" max="2"/>
+    <col width="31.21875" customWidth="1" min="3" max="4"/>
+    <col width="29.21875" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>28</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>questions</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>answer</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>page_num</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reterive the primary ntity or project name from the document metadata?,</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[Annexure B: Item Details: FURL OIL CONTROL &amp; TRIP VALVE &amp; Spares for MEL MAHAN STG II (2X800MW) UNIT-1 &amp; 2, Raigarh STPP Phase-II Unit-1&amp; Unit-2, APL RAIPUR U1 &amp; U2 &amp; MIRZAPUR MTEUPPL U1 &amp; U2 projects]: FURL OIL CONTROL &amp; TRIP VALVE &amp; Spares for MEL MAHAN STG II (2X800MW) UNIT-1 &amp; 2, Raigarh STPP Phase-II Unit-1&amp; Unit-2, APL RAIPUR U1 &amp; U2 &amp; MIRZAPUR MTEUPPL U1 &amp; U2 projects
+---
+[MAHAN 2x800 MW TPS]: MAHAN 2x800 MW TPS
+---
+[Annexure B: Item Details: FURL OIL CONTROL &amp; TRIP VALVE &amp; Spares for MEL MAHAN STG II (2X800MW) UNIT-1 &amp; 2, Raigarh STPP Phase-II Unit-1&amp; Unit-2, APL RAIPUR U1 &amp; U2 &amp; MIRZAPUR MTEUPPL U1 &amp; U2 projects]: FURL OIL CONTROL &amp; TRIP VALVE &amp; Spares for MEL MAHAN STG II (2X800MW) UNIT-1 &amp; 2, Raigarh STPP Phase-II Unit-1&amp; Unit-2, APL RAIPUR U1 &amp; U2 &amp; MIRZAPUR MTEUPPL U1 &amp; U2 projects</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>30, 59, 70</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reterive the scope for painting specifications?,</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[PS 9]: Components &gt;95°C uninsulated other than components coming in gas path. Temp: &gt;95°C &amp; &lt;400°C 24-807,820,860,865,867; 42-200,300; Instrument tappings, doors: 48-200,915; Heat Resistant Aluminium Paint to IS 13183 Gr. II DFT 20µm per coat DFT 20µm per coat
+---
+[K. PAINTING]: Epoxy coated</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21, 58</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the stream parameters such as flow, temperature, and pressure?,</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[O.FLOW DATA]: 1. Line Fluid | 2. Flow Max | 3. Normal in pr | 4. Allowable DP | 5. Actuator Sizing DP | 6. Temp Max | 7. Flow Temp | 8. Flow Sp Gravity | 9. Flow Viscosity | 10. Max Flow Cv | 11. Plug lift% | 12. Valve Cv | 13. Valve Closing Time Sec. | 14. Valve Opening Time Sec.Adjustable
+---
+[O.FLOW DATA]: 1.Line Fluid|2.Flow Max|3.Flow Min|4.Max Flow in Pr|5.Min Flow in Pr|6.Max Flow out Pr|7.Min Flow out Pr|8.Actuator Sizing DP|9.Temp Max|10.Flow Temp|11.Flow Sp Gravity|12.Flow Viscosity|13.Max / Min Flow Cv|14.plug Lifts @ max/minflow|%|%|15.Valve Cv / Cf
+---
+[O.FLOW DATA]: 1. Line Fluid | 2. Flow Max | 3. Normal in pr | 4. Allowable DP | 5. Actuator Sizing DP | 6. Temp Max | 7. Flow Temp | 8. Flow Sp Gravity | 9. Flow Viscosity | 10. Max Flow Cv | 11. Plug lift% | 12. Valve Cv | 13. Valve Closing Time Sec. | 14. Valve Opening Time Sec.Adjustable
+---
+[O.FLOW DATA]: 1. Line Fluid | 2. Flow Max | 3. Normal in pr | 4. Allowable DP | 5. Actuator Sizing DP | 6. Temp Max | 7. Flow Temp | 8. Flow Sp Gravity | 9. Flow Viscosity | 10. Max Flow Cv | 11. Plug lift% | 12. Valve Cv | 13. Valve Closing Time | 14. Valve Opening Time</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>22, 30, 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the water parameters such as flow, temperature, and pressure?,</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[O.FLOW DATA]: 1. Line Fluid | 2. Flow Max | 3. Normal in pr | 4. Allowable DP | 5. Actuator Sizing DP | 6. Temp Max | 7. Flow Temp | 8. Flow Sp Gravity | 9. Flow Viscosity | 10. Max Flow Cv | 11. Plug lift% | 12. Valve Cv | 13. Valve Closing Time | 14. Valve Opening Time
+---
+[O.FLOW DATA]: 1.Line Fluid | 2.Flow Max | 3.Flow Min | 4.Max Flow in Pr | 5.Min Flow in Pr | 6.Max Flow out Pr | 7. Min Flow out Pr | 8.Actuator Sizing DP | 9.Temp Max | 10.Flow Temp | 11.Flow Sp Gravity | 12.Flow Viscosity | 13.Max / Min Flow Cv | 14.plug Lifts @ max/minflow | 15.Valve Cv / Cf
+---
+[O.FLOW DATA]: 1. Line Fluid | 2. Flow Max | 3. Normal in pr | 4. Allowable DP | 5. Actuator Sizing DP | 6. Temp Max | 7. Flow Temp | 8. Flow Sp Gravity | 9. Flow Viscosity | 10. Max Flow Cv | 11. Plug Lift% | 12. Valve Cv | 13. Valve Closing Time | 14. Valve Opening Time</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10, 30, 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reterive Techcnical data from the general data of item?,</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[O.FLOW DATA]: 1. Line Fluid|2. Flow Max|3. Normal in pr|4. Allowable DP|5. Actuator Sizing DP|6. Temp Max|7. Flow Temp|8. Flow Sp Gravity|9. Flow Viscosity|10. Max Flow Cv|11. Plug lift%|12. Valve Cv|13. Valve Closing Time Sec.|14. Valve Opening Time Sec.Adjustable
+---
+[Trip Valves]: The vendor shall be an established supplier of Top &amp; bottom/ Top &amp; port/ post guided/ cage guided plug, Globe body, single seated with Pneumatic diaphragm actuated type trip valve, hereby referred as Trip valve, having adequate Engineering, Manufacturing, testing and servicing facilities and shall furnish technical backup documents in proof for above requirements. The vendor shall have experience of having supplied Trip valves as per the technical specification for anhydrous ammonia application or application of similar severity. Supply reference list with details of PO, PO date, customer name shall be submitted. The Trip valve offered shall be from the existing regular supply range of the vendor. Vendor shall provide the product catalogue. As proof of above pre-qualifying requirement points, vendor should submit: Their manufacturing product catalogue which lists the enquired Trip Valve as per above technical requirements. Vendor shall furnish general reference list with details of Customer name, fluid handled, Trip Valve parameter, P.O date, customer reference details wherein the vendor has supplied Trip Valves meeting the technical requirements as stated above. Minimum ONE end user certificate for the satisfactory operational performance of their supplied Trip Valve meeting the minimum pre-qualifying requirements stated above. OR Minimum Two past purchase orders of similar Trip Valves meeting the minimum pre-qualifying requirements stated above. Vendor to attach the corresponding data sheets/ technical documents of the Trip Valve supplied as per P.O / End user certificate (submitted vide point 4.c) for our review. In case of ordering, the Vendor shall have the responsibility for the following and same to be confirmed point wise. i) Vendor should have the component replacement responsibility in case of defect / failure. ii) Experts from Vendor's side shall associate in commissioning activities at site, if required. iii) Vendor should ensure the product performance during erection &amp; commissioning and ensure performance guarantee.
+---
+[Annexure B: Item Details: FURL OIL CONTROL &amp; TRIP VALVE &amp; Spares for MEL MAHAN STG II (2X800MW) UNIT-1 &amp; 2, Raigarh STPP Phase-II Unit-1&amp; Unit-2, APL RAIPUR U1 &amp; U2 &amp; MIRZAPUR MTEUPPL U1 &amp; U2 projects]: 104|138981675|40|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184414220002004|BURNER TRIP VALVES- LFO NB25|Burner Tripvalves _ LFO , NB25 as per the enclosed Spec. no.TOS:MEL:1350:/Rev.00 (TAG NOS. LO40A-LO40H, LO40J-LO40N, LO40P-LO40R)|16|NO|105|138981675|50|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184414220002005|BURNER TRIP VALVES- AIR SCAVENGING NB25|Burner Trip valves _ Scavenging air, NB 25 as per the enclosed Spec.no.TOS:MEL:1350:/Rev.00 (TAG NOS. A59A-A59H, A59J-A59N, A59P-A59R)|16|NO|106|138981675|60|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184414220002006|LFO RETURN BYPASS VALVE NB80|LFO RETURN BYPASS VALVE -LORBV (NB80; TAG NO.LO80) AS PER TECHNICAL SPECIFICATION TOS:MEL:1350/REV.00|1|NO|107|138981676|10|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184414220002001|LDO MAIN TRIP VALVE NB100|LDO MAIN TRIP VALVE AS PER THE ENCLOSED SPECIFICATION NO TOS:MEL:1350/00 TAG NO. LO30A;NB100.|1|NO|108|138981676|20|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184414220002002|LIGHT OIL (3 WAY) RETURN TRIP VALVE NB80|LIGHT OIL (3 WAY) RETURN TRIP VALVE AS PER THE ENCLOSED SPECIFICATION NO TOS:MEL:1350/00 TAG NO. LO45A;NB80.|1|NO|109|138981676|30|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184414220002003|BURNER TRIP VALVES- ATOMISING AIR NB25|Burner Trip valves _ Air , NB25 as per the enclosed Spec. no.TOS:MEL:1350:/Rev.00 (TAG NOS. A20A-A20H, A20J-A20N, A20P-R)|16|NO|110|138981676|40|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184414220002004|BURNER TRIP VALVES- LFO NB25|Burner Tripvalves _ LFO , NB25 as per the enclosed Spec. no.TOS:MEL:1350:/Rev.00 (TAG NOS. LO40A-LO40H, LO40J-LO40N, LO40P-LO40R)|16|NO|111|138981676|50|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184414220002005|BURNER TRIP VALVES- AIR SCAVENGING NB25|Burner Trip valves _ Scavenging air, NB 25 as per the enclosed Spec.no.TOS:MEL:1350:/Rev.00 (TAG NOS. A59A-A59H, A59J-A59N, A59P-A59R)|16|NO|112|138981676|60|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184414220002006|LFO RETURN BYPASS VALVE NB80|LFO RETURN BYPASS VALVE -LORBV (NB80; TAG NO.LO80) AS PER TECHNICAL SPECIFICATION TOS:MEL:1350/REV.00|1|NO|113|138981874|10|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184484298801001|ACTUATOR DIAPHRAGM FOR FO TRIP VALVES|Actuator Diaphragm for Trip valves against BHEL Material Codes: L184414220002001, L184414220002002 &amp; L184414220002006. 1 SET means 50% of total quantity in each variant of Actuator diaphragm required for replacement in the trip valves supplied against above said BHEL material codes.|1|SET|114|138981874|20|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184484298801002|GLAND PACKING FOR FO TRIP VALVES|Gland Packing for Trip valves against BHEL Material Codes: L184414220002001, L184414220002002 &amp; L184414220002006. 1 SET means 25% of total quantity in each variant of gland packing required for replacement in the trip valves supplied against above said BHEL material codes.|1|SET|115|138981874|30|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184484298801003|ACTUATOR DIAPHRAGM FOR BURNER TRIP VALVE|Actuator Diaphragm for Burner Trip valves against BHEL Material Codes: L184414220002003 to L184414220002005. 1 SET means 15% of total quantity in each variant of Actuator diaphragm required for replacement in the burner trip valves supplied against above said BHEL material codes.|1|SET|116|138981874|40|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184484298801004|GLAND PACKING FOR BURNER TRIP VALVES|Gland Packing for Burner Trip valves against BHEL Material Codes: L184414220002003 to L184414220002005. 1 SET means 15% of total quantity in each variant of gland packing required for replacement in the burner trip valves supplied against above said BHEL material codes.|1|SET|117|138981875|10|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184484298801001|ACTUATOR DIAPHRAGM FOR FO TRIP VALVES|Actuator Diaphragm for Trip valves against BHEL Material Codes: L184414220002001, L184414220002002 &amp; L184414220002006. 1 SET means 50% of total quantity in each variant of Actuator diaphragm required for replacement in the trip valves supplied against above said BHEL material codes.|1|SET|118|138981875|20|Package F (APL RAIPUR)|FOR APL RAIPUR Project site|L184484298801002|GLAND PACKING FOR FO TRIP VALVES|Gland Packing for Trip valves against BHEL Material Codes: L184414220002001, L184414220002002 &amp; L184414220002006. 1 SET means 25% of total quantity in each variant of gland packing required for replacement in the trip valves supplied against above said BHEL material codes.|1|SET
+---
+[90]: SI No: 90 | PR No: 137954357 | PR Item: 40 | Package: Package C (Raigarh STPP) | Delivery Location: BHEL Trichy stores | Material Code: L1842S4299702004 | Material Description: AIR FILTER REGULATOR | Long Description: This pneumatic air filter regulator shall be exactly same as the pneumatic air filter regulator of Control Valve as offered for this project for PGMA 42-200 for check list no.01 for customer nos.1842 &amp; 1843. One set means 5 % of each type / model/ rating of air filter regulator of control valve released for this project under material code L184214220001001 | QTY: 1 | UOM: SET</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3, 30, 66, 67</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the operating and mechanical data for the stream condition rating?,</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[V. TECHNICAL REQUIREMENTS]: 1|Flow Parameters|For Flow Parameters and requirement of accessories refer to Item Description and/or the Vendor Check List. 2|Operating Criteria|At 80% opening of valve flow max, stem travel of 80% at max. Flow condition and stem travel of 20% at min. flow condition. 3|Capacity|120% of max. flow handling capacity. 4|Percentage of stem Travel from min. Flow to max. Flow|Shall not be less than 50%. 5|Sizing criteria|As per ISA Hand Book with measures to avoid choked flow. 6|Outlet velocity|Max. 150 m/sec. for steam and 8 m/sec. for liquid. 50% of sonic velocity for flashing services. 7|Noise|Valve internal shall not vibrate or chatter and not unduly noisy. The noise level shall be limited to max. 85 dB at 1 mtr. From valve surface.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the operating and mechanical data for the stream condition size?,</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[V. TECHNICAL REQUIREMENTS]: 1|Flow Parameters|For Flow Parameters and requirement of accessories refer to Item Description and/or the Vendor Check List. 2|Operating Criteria|At 80% opening of valve flow max, stem travel of 80% at max. Flow condition and stem travel of 20% at min. flow condition. 3|Capacity|120% of max. flow handling capacity. 4|Percentage of stem Travel from min. Flow to max. Flow|Shall not be less than 50%. 5|Sizing criteria|As per ISA Hand Book with measures to avoid choked flow. 6|Outlet velocity|Max. 150 m/sec. for steam and 8 m/sec. for liquid. 50% of sonic velocity for flashing services. 7|Noise|Valve internal shall not vibrate or chatter and not unduly noisy. The noise level shall be limited to max. 85 dB at 1 mtr. From valve surface.
+---
+[A. VALVE BODY]: 1. Make/Type No: Vendor to state | 2. Line Size mm: OD 88.9x5.49 | 3. Body/port Size mm: NB : 80 | 4. Plug Travel mm: Vendor to state | 5. Body Style / Rating: ANSI 300 LBS | NP | 6. Ends: 3" Flange ANSI 300 LBS | 7. Port: Single / Double | 8. Guiding: Stem / Port (Vendor to state) | 9. Body Matl: Cast or forged carbon steel | 10. Trim No: Vendor to state | 11. Plug Matl: ANSI | 12. Steam Size/Matl: Vendor to state | 13. Seat Matl: Vendor to state | 14. Cage Matl,if any: Vendor to state | 15. Plug/Cage Style: = % | 16. Seat Leak Class: As per ANSI B 16.104 / FCI 70-2-V | 17. Plug pushdown to: Close | 18. Flow Tends to: Open | 19. Bonnet / packing: STD / Extended | 20. Drain plug: Vendor to state | 21. Noise Level: &lt;85dBA @1m distance
+---
+[A. VALVE BODY]: Line Size: ODXT mm | Body/port Size: Nb mm | Plug Travel: Mm | Body Style / Rating: NP | Ends: Flanged to : | Guiding: Cage or Top &amp; Bottom | Body Material: Carbon Steel, ASTM A216 WCB | Trim No: | Plug Matl: | Steam Size/Material: | Seat, Material: | Cage Material: | Plug/Gauge Style: VI to ANSI FCI 70-2 | Seat Leak Class: | Plug pushdown to: | Flow Tends to: | Bonnet / packing: | Lub/Isol Valve: | Drain Valve: | Noise Level: </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>10, 35, 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What is the spray water body material?,</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[A. VALVE BODY]: Carbon Steel, ASTM A216 WCB
+---
+[A. VALVE BODY]: Carbon Steel, ASTM A216 WCB
+---
+[A. VALVE BODY]: Carbon Steel, ASTM A216 WCB</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>10, 14, 22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What is the spray water trim?,</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[12]: Quick changing, removable through top after bonnet removal without cutting
+---
+[87]: VALVE TRIM|Package C (Raigarh STPP)|BHEL Trichy stores|L1842S4299702001|This Valve trim (including cage,plug, stem, seat rings, guide bushings etc.) shall be exactly same as the valve trim of Control Valve as offered for this project for PGMA 42-200 for check list no.01 for customer nos.1842 &amp; 1843. One set means 1 set for each type of control valve released for this project under material code L184214220001001|1|SET
+---
+[125]: VALVE TRIM|Package E (APL RAIPUR)|BHEL Trichy stores|L1844S4299702001|This Valve trim (including cage,plug, stem, seat rings, guide bushings etc.) shall be exactly same as the valve trim of Control Valve as offered for this project for PGMA 42-200 for check list no.01 for customer nos.1844 &amp; 1845. One set means 1 set for each type of control valve released for this project under material code L184414220001001</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>36, 65, 68</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What is the spray water size?,</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[A. VALVE BODY]: Line Size mm: OD 88.9 X 5.49 t | Body/port Size mm: NB: 80
+---
+[A. VALVE BODY]: Line Size mm: OD 114.3 x 6.02 t
+---
+[A. VALVE BODY]: Line Size mm: OD 114.3 x 6.02 t</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>11, 15, 19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reterivet the technical table data of spray water actuator and their types,</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[B. ACTUATOR ASSY]: B. ACTUATOR ASSY|1. Make/Type No||2. Style||3. Size/Volume||4. Diaphragm Matl||5.Spring No/Range||6. Spring No/Range||7. Air to||8. Signal pr||9. Pr port Conn||10. On Air Failure|Stay Put||11. Lockup Valve type No|BHEL scope||12. Lockup Valve Set pr||S.NO|ITEM|O &amp; M Manual|Spares identifier Catalog&amp;Spec|3|A||4|B||5|B 11||6|C||7|D||8|E||9|F||10|G
+---
+[B.ACTUATOR ASSY]: B.ACTUATOR ASSY|1.Make / type no||2.Style||3.Size/Volume||4.Diaphragm Matl||5. Port Size|1/4 " NPT|6.Spring no / Range||7.Spring To||8. Air To||9. Signal Pr.||10. Handwheel||11. On Air Failure|Stay Put|12.Lockup Valve Type no||13. Lockup Valve Set Pr.S
+---
+[B. ACTUATOR ASSY]: B. ACTUATOR ASSY|1. Make/Type No|Vendor to specify|2. Style|Vendor to specify|3. Size/Volume|Vendor to specify|4. Diaphragm Material|Vendor to specify|5. Spring No/Range|Vendor to specify|6. Spring to|Close|7. Air to|Open|8. Signal pr|Vendor to specify|9. Pr port Conn|Vendor to specify|10. On Air Failure|Stay Put|11. Lockup Valve type no.|NOT REQD. - BHEL scope|12. Lockup Valve Set pr|Vendor to specify</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>30, 32, 44</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the accessories?,</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[87]: VALVE TRIM|Package C (Raigarh STPP)|BHEL Trichy stores|L1842S4299702001|This Valve trim (including cage,plug, stem, seat rings, guide bushings etc.) shall be exactly same as the valve trim of Control Valve as offered for this project for PGMA 42-200 for check list no.01 for customer nos.1842 &amp; 1843. One set means 1 set for each type of control valve released for this project under material code L184214220001001|1|SET
+---
+[I. TERMINAL BOX]: Provided as per the sketch enclosed | NEMA 4 &amp; 13,DUST TIGHT &amp; OIL TIGHT | Vendor to specify | Commissioning/Customer
+---
+[PS2]: Loose tubes, SH, RH &amp; Eco. coils
+---
+[Annexure B: Item Details: FURL OIL CONTROL &amp; TRIP VALVE &amp; Spares for MEL MAHAN STG II (2X800MW) UNIT-1 &amp; 2, Raigarh STPP Phase-II Unit-1&amp; Unit-2, APL RAIPUR U1 &amp; U2 &amp; MIRZAPUR MTEUPPL U1 &amp; U2 projects]: SOLENOID VALVES | POSITION FEEDBACK LIMIT SWITCH | AIR FILTER REGULATORS | DIAPHRAGM | GLAND PACKING | PLUG, SEAT, CAGE, STEM ETC. | RETAINER RING, SEAL RING ETC. | GASKET | SOLENOID COIL FOR PNEU TYPE ON/OFF VLV | AIR LOCK RELAY | SIGNAL AIR BOOSTER UNIT</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>32, 58, 60, 65</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the inspection and NDT requirements?,</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[M.TEST CERTIFICATES]: 1.Hydraulic test | Vendor to specify | 2.Seat leak test | Vendor to specify | 3.Material certificates | Vendor to specify | 4.Std. test on Actuator | Vendor to specify | 5.Dimentional test | Vendor to specify
+---
+[M.TEST CERTIFICATES]: 1.Hydraulic test | Vendor to specify | 2.Seat leak test | Vendor to specify | 3.Material certificates | Vendor to specify | 4.Std. test on Actuator | Vendor to specify | 5.Dimentional test | Vendor to specify
+---
+[Note to Vendor]: Taking care of the above indicated technical requirements in full, vendor to submit signed &amp; sealed copy of Sub-delivery enquiry deviation (SDED) format sent along with the purchase enquiry, without any deviations, quoting the document reference. Any deviation in the technical requirements has to be indicated only in the SDED format. Other than the SDED format, hidden deviations indicated elsewhere in the offer will not be considered.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>21, 33, 51</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the buyer’s terms of payment?,</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[5]: The buyer’s terms of payment require the Vendor / Contractor / Supplier to forthwith and immediately pay to the Employer any sum or sums up to a maximum amount of Rs ----------------- (Rupees ------------------------) without any demur, immediately on first demand from the Employer and without any reservation, protest, and recourse and without the Employer needing to prove or demonstrate reasons for its such demand. Any such demand made on the Bank shall be conclusive as regards the amount due and payable by the Bank under this guarantee. However, our liability under this guarantee shall be restricted to an amount not exceeding Rs. _______________. We undertake to pay to the Employer any money so demanded notwithstanding any dispute or disputes raised by the Vendor / Contractor / Supplier in any suit or proceeding pending before any Court or Tribunal, Arbitrator or any other authority, our liability under this present being absolute and unequivocal.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What is the SSC delivery schedule?,</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[07 DELIVERY:]: Delivery shall be as follows 1.MEL MAHAN: 120 days from Manufacturing clearance 2.Raigarh STPP: 150 days from Manufacturing clearance 3.APL RAIPUR: 180 days from Manufacturing clearance 4.MIRZAPUR MTEUPPL: 210 Days from Manufacturing clearance Package Details as per Annexure B . (including Manufacturing, Inspection, Packing, Forwarding and delivery at project site/Trichy stores). Note: Delivery period mentioned elsewhere in the GeM Bid document shall be ignored and the delivery period shall be as per this clause.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What is included in the price format?,</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[Note to Vendor]: Taking care of the above indicated technical requirements in full, vendor to submit signed &amp; sealed copy of Sub-delivery enquiry deviation (SDED) format sent along with the purchase enquiry, without any deviations, quoting the document reference. Any deviation in the technical requirements has to be indicated only in the SDED format. Other than the SDED format, hidden deviations indicated elsewhere in the offer will not be considered.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What is the warranty for SSC?,</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[]: No relevant information found
+---
+[]: No relevant information found
+---
+[3 | MAHAN 2x800 MW TPS]: No relevant information found
+---
+[4]: No relevant information found
+---
+[No relevant information found]: No relevant information found</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>6, 58, 65, 108, 109</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the contractor liquidated damages?,</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[18]: LIQUIDATED DAMAGE: Liquidated Damages, wherever referred under this Tender/Agreement, shall mean and refer to the damages, not in the nature of penalty, which the contractor agrees to pay in the event of delay in delivery of supplies, breach of contract etc. as the case may be. Liquidated Damages leviable upon the Supplier/Vendor is a sum which is agreed by the parties as a reasonable and genuine pre-estimate of damages which will be suffered by BHEL on account of delay/breach on the part of the Supplier/Vendor. If the Seller/Service Provider fails to deliver any or all of the Goods/Services within the original/re-fixed delivery period(s) specified in the contract/PO, the Buyer/BHEL will be entitled to deduct/recover the Liquidated Damages for the delay, unless covered under Force Majeure conditions aforesaid, @ 0.5% of the contract value of delayed quantity per week or part of the week of delayed period as pre-estimated damages not exceeding 10% of the contract value of delayed quantity without any controversy/dispute of any sort whatsoever. LD shall be reckoned from the Contract delivery date to material receipt date.
+---
+[Section 4 - Compensation for Damages]: If the Principal has terminated the contract according to Section 3, or if the Principal is entitled to terminate the contract according to section 3, the Principal shall be entitled to demand and recover from the Contractor liquidated damages equivalent to 5% of the contract value or the amount equivalent to Security Deposit/ Performance Bank Guarantee, whichever is higher.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>85, 99</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the quality control and inspection testing?,</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[6. Backup document checklist to meet PQR to the fullest satisfaction of BHEL:]: Clause 1: i) ISO or Other third Party certification about the engineering, manufacturing, testing and servicing facilities in the name of supplier/OEM as applicable. The certificate shall be specific for the product quoted by the vendor. ii) List of manufacturing, testing and servicing facilities available (like machinery/equipment) in the letterhead of supplier/OEM as applicable. Clause 2: Supply reference list with details of PO, PO date, customer name, application severity/type in the form of a table. Clause 3: Product Catalogue in the name of supplier/OEM as applicable. Clause 4: Min. one end user certificate (or) Two POs in the name of supplier/OEM as applicable. Clause 5: Signed copy of this technical PQR document
+---
+[06]: INSPECTION / INSPECTION &amp; TESTING AT SUPPLIERS WORKS: Inspection and testing requirements are to be carried out as per the specification and BHEL/Customer approved Drawing (All documents shall be submitted within 15 days from the date of PO for our approval), Technical spec &amp; QP and all test certificates are to be submitted in complete set. BHEL reserves the right to inspect the material during manufacturing and also to get tested the material under dispatch from third party. The test results of third party test shall be final and binding on the Supplier/Vendor. BHEL will reserve the right to inspect/test the material during/after manufacturing at suppliers' works, and/or at BHEL Site. In case of rejection at any stage, Supplier/Vendor shall be liable to replace the materials at his own cost.
+---
+[X. INWARD INSPECTION]: Verify the Works Test Certificates, Marking Particulars, Name Plates of each accessory and the scope of supply. Watch for damages. Perform random check on all terminal connections and the internal particulars.
+---
+[6. Backup document checklist to meet PQR to the fullest satisfaction of BHEL:]: Clause 1: i) ISO or Other third Party certification about the engineering, manufacturing, testing and servicing facilities in the name of supplier/OEM as applicable. The certificate shall be specific for the product quoted by the vendor. ii) List of manufacturing, testing and servicing facilities available (like machinery/equipment) in the letterhead of supplier/OEM as applicable. Clause 2: Supply reference list with details of PO, PO date, customer name, application severity/type in the form of a table. Clause 3: Product Catalogue in the name of supplier/OEM as applicable. Clause 4: Min. one end user certificate (or) Two POs in the name of supplier/OEM as applicable. Clause 5: Signed copy of this technical PQR document
+---
+[22 Test reports &amp; Catalogues]: 1. Test Certificates as per Manufacturer's Standard. 2. SMART positioner catalogues &amp; O&amp;M manuals.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>34, 39, 50, 80</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reterive the data fro approval?,</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[Approved]: Approved: D. Kavitha
+---
+[6. Backup document checklist to meet PQR to the fullest satisfaction of BHEL:]: S. No | Document description | Check list
+a. | Back-up documents as per pt. 1 | ☐
+b. | Product Catalogues as per pt. 4a | ☐
+c. | General reference list as per pt. 4b | ☐
+d. | One end user certificate OR Two P.O as per pt. 4c | ☐
+e. | Data sheets/ technical documents as per pt. 4d | ☐
+f. | Confirmation to clause (5) | ☐
+---
+[4.2.15]: In the event of any ambiguity in GST law with respect to availability of input credit of GST charged on the invoice raised by the contractor or with respect to any other matter having impact on BHEL, BHEL’s decision shall be final and binding on the Supplier/Vendor.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3, 47, 79</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What are the packing and dispatch requirements for bidders?,</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[07 DELIVERY:]: Delivery shall be as follows 1.MEL MAHAN: 120 days from Manufacturing clearance 2.Raigarh STPP: 150 days from Manufacturing clearance 3.APL RAIPUR: 180 days from Manufacturing clearance 4.MIRZAPUR MTEUPPL: 210 Days from Manufacturing clearance Package Details as per Annexure B. (including Manufacturing, Inspection, Packing, Forwarding and delivery at project site/Trichy stores). Note: Delivery period mentioned elsewhere in the GeM Bid document shall be ignored and the delivery period shall be as per this clause.
+---
+[PACKING REQ: -]: 1. ALL OPENINGS (FLUID, PNEUMATIC &amp; ELECTRIC) SHALL BE FIRMLY CAPPED. 2. ITEM SHALL BE PACKED IN WOODEN BOXES WITH WATER PROOF UNDER COVER. 3. PACKING AND STRUTS SHALL BE USED TO ARREST ROLLING OF ITEMS AND TO AVOID TRANSIT DAMAGE. 4. LIMIT SWITCHES AND SUCH COMPONENTS SHALL BE ENCAPSULATED PROPERLY WITH THERMOCOLE.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>77, 80</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    What is the compliance certificate for Clause 20(B)?,</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[xvii. Declaration regarding compliance to Restrictions under Rule 144 (xi) of GFR 2017 as per Annexure – 13]: Declaration regarding compliance to Restrictions under Rule 144 (xi) of GFR 2017 as per Annexure – 13
+---
+[20 Electro Magnetic Compatibility]: SMART positioner shall conform to EMC requirements as per the relevant international standards IEC/EN.
+---
+[05]: MATERIAL DISPATCH CLEARANCE CERTIFICATE (MDCC): MDCC shall be issued by BHEL. No material shall be dispatched by supplier unless and until Material Dispatch Clearance Certificate (MDCC) issued by BHEL Site. In case any material is dispatched without MDCC and any loss is incurred by Supplier/Vendor for any reason whatsoever, BHEL shall not be responsible in any manner to compensate the supplier in this regard.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2, 49, 80</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reterive the pre-qulification of independent laboratory,</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[II B]: Smart positioner to be supplied as per technical specification TDC:TCI: 317/Rev. 07 &amp; E,C&amp;I input for Control Valve accessories for Mahan project (Cust no. 1832-1833)( CI: MAHAN: ECI:CV, Rev. 00)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    reterive the compensation damages,</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[18]: LIQUIDATED DAMAGE: Liquidated Damages, wherever referred under this Tender/Agreement, shall mean and refer to the damages, not in the nature of penalty, which the contractor agrees to pay in the event of delay in delivery of supplies, breach of contract etc. as the case may be. Liquidated Damages leviable upon the Supplier/Vendor is a sum which is agreed by the parties as a reasonable and genuine pre-estimate of damages which will be suffered by BHEL on account of delay/breach on the part of the Supplier/Vendor. If the Seller/Service Provider fails to deliver any or all of the Goods/Services within the original/re-fixed delivery period(s) specified in the contract/PO, the Buyer/BHEL will be entitled to deduct/recover the Liquidated Damages for the delay, unless covered under Force Majeure conditions aforesaid, @ 0.5% of the contract value of delayed quantity per week or part of the week of delayed period as pre-estimated damages not exceeding 10% of the contract value of delayed quantity without any controversy/dispute of any sort whatsoever. LD shall be reckoned from the Contract delivery date to material receipt date.
+---
+[4.2.9]: Any financial loss arises to BHEL on account of failure or delay in submission of any document as per contract/purchase order/work order at the time of submission of Tax invoice to BHEL, shall be deducted from Supplier/Vendor’s bill or otherwise as deemed fit.
+---
+[Section 4 - Compensation for Damages]: 4.1 If the Principal has disqualified the Bidder from the tender process prior to the award according to Section 3, the Principal is entitled to demand and recover the damages equivalent Earnest Money Deposit/ Bid Security. 4.2 If the Principal has terminated the contract according to Section 3, or if the Principal is entitled to terminate the contract according to section 3, the Principal shall be entitled to demand and recover from the Contractor liquidated damages equivalent to 5% of the contract value or the amount equivalent to Security Deposit/ Performance Bank Guarantee, whichever is higher.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>79, 85, 99</t>
+        </is>
       </c>
     </row>
   </sheetData>
